--- a/Excel_luban/Datas/__tables__.xlsx
+++ b/Excel_luban/Datas/__tables__.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -176,13 +176,25 @@
   </si>
   <si>
     <t>Script_Language.xlsx</t>
+  </si>
+  <si>
+    <t>TbPuzzleMapConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PuzzleMapConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PuzzleMapConfig.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +212,14 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -241,7 +261,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -249,6 +269,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -527,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -671,63 +694,77 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
+        <v>48</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>38</v>
+      <c r="E7" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>